--- a/artfynd/A 18760-2023 artfynd.xlsx
+++ b/artfynd/A 18760-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18760-2023 artfynd.xlsx
+++ b/artfynd/A 18760-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80984022</v>
+        <v>80984035</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>822112.2028375585</v>
+        <v>822122</v>
       </c>
       <c r="R2" t="n">
-        <v>7329005.858345765</v>
+        <v>7328872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80984040</v>
+        <v>86995369</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossabäcken, Nb</t>
+          <t>Mossabäcken Ö (Pålträsket), Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>822012.0060597023</v>
+        <v>822012</v>
       </c>
       <c r="R3" t="n">
-        <v>7329057.066661449</v>
+        <v>7329061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,53 +853,62 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövrik skog, kulturmark, ung</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Granlåga 30 cm</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80984019</v>
+        <v>80984028</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>822069.9522439331</v>
+        <v>822026</v>
       </c>
       <c r="R4" t="n">
-        <v>7328600.856995021</v>
+        <v>7329240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +951,9 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80984028</v>
+        <v>86995371</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,14 +1011,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossabäcken, Nb</t>
+          <t>Mossabäcken Ö (Pålträsket), Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>822026.300094084</v>
+        <v>822031</v>
       </c>
       <c r="R5" t="n">
-        <v>7329239.829718779</v>
+        <v>7329175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,31 +1061,40 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik skog, kulturmark, ung</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asp 32 cm</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80984035</v>
+        <v>80984019</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>822122.0445874566</v>
+        <v>822070</v>
       </c>
       <c r="R6" t="n">
-        <v>7328871.932093914</v>
+        <v>7328601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1159,9 @@
           <t>2019-10-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,50 +1188,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>86995371</v>
+        <v>80984022</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mossabäcken Ö (Pålträsket), Nb</t>
+          <t>Mossabäcken, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>822031.192124893</v>
+        <v>822112</v>
       </c>
       <c r="R7" t="n">
-        <v>7329174.928312886</v>
+        <v>7329006</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,80 +1269,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövrik skog, kulturmark, ung</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Asp 32 cm</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
-        </is>
-      </c>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86995369</v>
+        <v>91839086</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mossabäcken Ö (Pålträsket), Nb</t>
+          <t>Mossabäcken, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>822011.9517867861</v>
+        <v>822037</v>
       </c>
       <c r="R8" t="n">
-        <v>7329061.177469298</v>
+        <v>7328870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,22 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,145 +1366,19 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lövrik skog, kulturmark, ung</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Granlåga 30 cm</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>91839086</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mossabäcken, Nb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>822036.9301262649</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7328870.096138306</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
           <t>Frédéric Forsmark</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18760-2023 artfynd.xlsx
+++ b/artfynd/A 18760-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984035</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86995369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984028</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>Karelsk barkfluga och andra naturvårdsintressanta arter i lövrik skog i Norrbotten 2020</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86995371</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984022</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91839086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>